--- a/database.xlsx
+++ b/database.xlsx
@@ -490,7 +490,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
